--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Email</t>
   </si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>EldonTrantow@yopmail.com</t>
+  </si>
+  <si>
+    <t>VeolaConsidine@yopmail.com</t>
+  </si>
+  <si>
+    <t>YvoneBerge@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1255,7 +1261,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1373,6 +1379,16 @@
         <v>22</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Email</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>EldonTrantow@yopmail.com</t>
+  </si>
+  <si>
+    <t>TwylaBosco@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1255,7 +1258,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1373,6 +1376,11 @@
         <v>22</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Email</t>
   </si>
@@ -96,6 +96,24 @@
   </si>
   <si>
     <t>EldonTrantow@yopmail.com</t>
+  </si>
+  <si>
+    <t>RhiannonWitting@yopmail.com</t>
+  </si>
+  <si>
+    <t>ReidDoyle@yopmail.com</t>
+  </si>
+  <si>
+    <t>MarlinHellerJr@yopmail.com</t>
+  </si>
+  <si>
+    <t>BurtonBatz@yopmail.com</t>
+  </si>
+  <si>
+    <t>BradRyan@yopmail.com</t>
+  </si>
+  <si>
+    <t>AllegraMcClure@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1255,7 +1273,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1373,6 +1391,36 @@
         <v>22</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>Email</t>
   </si>
@@ -114,6 +114,48 @@
   </si>
   <si>
     <t>AllegraMcClure@yopmail.com</t>
+  </si>
+  <si>
+    <t>ElijahWisoky@yopmail.com</t>
+  </si>
+  <si>
+    <t>MrDwightRenner@yopmail.com</t>
+  </si>
+  <si>
+    <t>SarahKovacek@yopmail.com</t>
+  </si>
+  <si>
+    <t>IsraelOConner@yopmail.com</t>
+  </si>
+  <si>
+    <t>EllisKemmer@yopmail.com</t>
+  </si>
+  <si>
+    <t>SukWaters@yopmail.com</t>
+  </si>
+  <si>
+    <t>JodieGreen@yopmail.com</t>
+  </si>
+  <si>
+    <t>JackMcCulloughV@yopmail.com</t>
+  </si>
+  <si>
+    <t>DonnieMcKenzie@yopmail.com</t>
+  </si>
+  <si>
+    <t>KenethHarris@yopmail.com</t>
+  </si>
+  <si>
+    <t>MsMaymeRempel@yopmail.com</t>
+  </si>
+  <si>
+    <t>CareyWunschMD@yopmail.com</t>
+  </si>
+  <si>
+    <t>MrsLionelSchmeler@yopmail.com</t>
+  </si>
+  <si>
+    <t>LawrenceAltenwerth@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1273,7 +1315,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1421,6 +1463,76 @@
         <v>28</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="UserData" sheetId="1" r:id="rId1"/>
+    <sheet name="YouthClubMembers" r:id="rId5" sheetId="2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="120">
   <si>
     <t>Email</t>
   </si>
@@ -102,6 +103,291 @@
   </si>
   <si>
     <t>YvoneBerge@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth3@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth1@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth2@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth4@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth5@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth6@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth7@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth9@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth8@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth10@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth11@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth12@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth13@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth14@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth15@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth16@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth18@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth17@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth19@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth20@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth21@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth23@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth24@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth22@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth25@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth27@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth26@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth30@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth29@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth28@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth33@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth32@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth31@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth35@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth36@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth34@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth37@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth38@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth39@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth40@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth41@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth42@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth44@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth43@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth45@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth48@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth46@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth51@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth49@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth52@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth53@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth54@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth56@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth57@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth55@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth60@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth59@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth58@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth63@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth61@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth62@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth66@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth65@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth64@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth68@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth67@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth69@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth72@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth70@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth71@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth74@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth73@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth77@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth75@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth76@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth79@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth78@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth80@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth86@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth85@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth84@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth89@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth88@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth90@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth91@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth92@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth95@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth93@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth94@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth96@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth97@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth98@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth99@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth100@yopmail.com</t>
+  </si>
+  <si>
+    <t>nnnyouth101@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1393,4 +1679,494 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A96"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="0">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="0">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="0">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="0">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="0">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="0">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="0">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="0">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="0">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="0">
+        <v>119</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>Email</t>
   </si>
@@ -165,6 +165,9 @@
   </si>
   <si>
     <t>GeneReilly@yopmail.com</t>
+  </si>
+  <si>
+    <t>AnnisDenesik@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1324,7 +1327,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A46"/>
+  <dimension ref="A1:A47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1557,6 +1560,11 @@
         <v>45</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>Email</t>
   </si>
@@ -156,18 +156,6 @@
   </si>
   <si>
     <t>LawrenceAltenwerth@yopmail.com</t>
-  </si>
-  <si>
-    <t>SamellaDaniel@yopmail.com</t>
-  </si>
-  <si>
-    <t>CurtSkiles@yopmail.com</t>
-  </si>
-  <si>
-    <t>GeneReilly@yopmail.com</t>
-  </si>
-  <si>
-    <t>AnnisDenesik@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1327,7 +1315,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1545,26 +1533,6 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="s" s="0">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="0">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="0">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="0">
-        <v>46</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>rohank90020@maildrop.cc</t>
   </si>
@@ -137,6 +137,24 @@
   </si>
   <si>
     <t>rohank90061@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90064@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90063@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90062@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90067@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90066@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90065@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1546,7 +1564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A43"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1768,6 +1786,36 @@
         <v>40</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
   <si>
     <t>rohank90020@maildrop.cc</t>
   </si>
@@ -191,6 +191,126 @@
   </si>
   <si>
     <t>rohank90077@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90085@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90084@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90081@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90080@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90086@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90087@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90088@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90090@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90091@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90089@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90092@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90093@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90094@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90095@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90096@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90097@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90100@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90099@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90098@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90101@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90103@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90102@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90105@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90104@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90106@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90108@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90107@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90109@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90112@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90110@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90111@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90114@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90113@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90115@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90117@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90118@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90116@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90121@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90119@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90120@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1605,7 +1725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A60"/>
+  <dimension ref="A1:A100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,6 +2032,206 @@
         <v>58</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="0">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="0">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="0">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="0">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="0">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="0">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="0">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="0">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="0">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="0">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="0">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="0">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
   <si>
     <t>rohank90020@maildrop.cc</t>
   </si>
@@ -494,6 +494,24 @@
   </si>
   <si>
     <t>yco44168@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco54875@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco54876@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco54878@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco54877@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco54879@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco54880@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1908,7 +1926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A161"/>
+  <dimension ref="A1:A167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2720,6 +2738,36 @@
         <v>159</v>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="s" s="0">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="0">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="0">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="0">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="0">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="0">
+        <v>165</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="172">
   <si>
     <t>rohank90020@maildrop.cc</t>
   </si>
@@ -512,6 +512,24 @@
   </si>
   <si>
     <t>yco54880@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco65473@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco65472@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco65475@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco65474@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco65477@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco65476@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1926,7 +1944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A167"/>
+  <dimension ref="A1:A173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2768,6 +2786,36 @@
         <v>165</v>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="s" s="0">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="0">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="0">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="0">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="0">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="0">
+        <v>171</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,522 +14,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="9">
   <si>
-    <t>rohank90020@maildrop.cc</t>
+    <t>yco71304@maildrop.cc</t>
   </si>
   <si>
-    <t>rohank90021@maildrop.cc</t>
+    <t/>
   </si>
   <si>
-    <t>rohank90022@maildrop.cc</t>
+    <t>yco71303@maildrop.cc</t>
   </si>
   <si>
-    <t>rohank90025@maildrop.cc</t>
+    <t>yco71306@maildrop.cc</t>
   </si>
   <si>
-    <t>rohank90023@maildrop.cc</t>
+    <t>yco71305@maildrop.cc</t>
   </si>
   <si>
-    <t>rohank90024@maildrop.cc</t>
+    <t>yco71308@maildrop.cc</t>
   </si>
   <si>
-    <t>rohank90028@maildrop.cc</t>
+    <t>yco71307@maildrop.cc</t>
   </si>
   <si>
-    <t>rohank90026@maildrop.cc</t>
+    <t>Sankalp Vihar Alpha Youth Club</t>
   </si>
   <si>
-    <t>rohank90027@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90030@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90029@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90031@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90032@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90033@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90034@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90036@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90035@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90037@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90040@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90039@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90038@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90043@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90041@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90042@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90046@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90044@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90045@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90048@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90047@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90049@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90051@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90052@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90055@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90053@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90054@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90057@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90058@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90056@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90059@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90060@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90061@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90064@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90063@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90062@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90067@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90066@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90065@maildrop.cc</t>
-  </si>
-  <si>
-    <t>HassieBrown@yopmail.com</t>
-  </si>
-  <si>
-    <t>rohank90069@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90068@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90071@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90072@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90073@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90076@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90075@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90074@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90078@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90079@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90077@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90085@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90084@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90081@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90080@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90086@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90087@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90088@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90090@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90091@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90089@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90092@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90093@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90094@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90095@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90096@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90097@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90100@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90099@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90098@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90101@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90103@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90102@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90105@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90104@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90106@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90108@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90107@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90109@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90112@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90110@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90111@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90114@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90113@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90115@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90117@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90118@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90116@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90121@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90119@maildrop.cc</t>
-  </si>
-  <si>
-    <t>rohank90120@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000002@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000003@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000001@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000006@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000004@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000005@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000007@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000008@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000009@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000012@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000010@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000011@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000014@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000015@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000013@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000018@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000016@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000017@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000021@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000019@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000020@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000024@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000023@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000022@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000026@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000025@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000027@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000028@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000030@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000029@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000031@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000033@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000032@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000035@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000034@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yc000036@maildrop.cc</t>
-  </si>
-  <si>
-    <t>ycc00002@maildrop.cc</t>
-  </si>
-  <si>
-    <t>ycc00001@maildrop.cc</t>
-  </si>
-  <si>
-    <t>ycc00004@maildrop.cc</t>
-  </si>
-  <si>
-    <t>ycc00003@maildrop.cc</t>
-  </si>
-  <si>
-    <t>ycc00005@maildrop.cc</t>
-  </si>
-  <si>
-    <t>ycc00006@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco41921@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco41920@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco41922@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco41923@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco41925@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco41924@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco43185@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco43184@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco43186@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco43187@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco43188@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco43189@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco44162@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco44161@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco44163@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco44165@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco44166@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco44167@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco44168@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco54875@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco54876@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco54878@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco54877@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco54879@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco54880@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco65473@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco65472@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco65475@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco65474@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco65477@maildrop.cc</t>
-  </si>
-  <si>
-    <t>yco65476@maildrop.cc</t>
+    <t>Picked</t>
   </si>
 </sst>
 </file>
@@ -1929,8 +1440,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="s" s="0">
-        <v>47</v>
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t>HassieBrown@yopmail.com</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1944,876 +1457,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A173"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" t="inlineStr" s="0">
         <is>
           <t>Email</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr" s="0">
+        <is>
+          <t>Youth Club Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="0">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr" s="0">
-        <is>
-          <t>rohank90019@maildrop.cc</t>
-        </is>
+      <c r="A2" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
         <v>6</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
+      <c r="B7" t="s" s="0">
         <v>7</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="0">
+      <c r="C7" t="s" s="0">
         <v>8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="0">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="0">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="0">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="0">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="0">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="0">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="0">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="0">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="0">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="0">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="0">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="0">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="0">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="0">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="0">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="0">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="0">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="0">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="0">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="0">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="0">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="0">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="0">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="0">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="0">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="0">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="0">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="0">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="0">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="0">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="0">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="0">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="0">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="0">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="0">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="0">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="0">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="0">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="0">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="0">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="0">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="0">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="0">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="0">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="0">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="0">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="0">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="0">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="0">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="0">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="0">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="0">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="0">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="0">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="0">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s" s="0">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="0">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="0">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="0">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s" s="0">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s" s="0">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s" s="0">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s" s="0">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="0">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s" s="0">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s" s="0">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="0">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s" s="0">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s" s="0">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s" s="0">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="0">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s" s="0">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="0">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="0">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s" s="0">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s" s="0">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s" s="0">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s" s="0">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s" s="0">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s" s="0">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s" s="0">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s" s="0">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s" s="0">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s" s="0">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s" s="0">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s" s="0">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s" s="0">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s" s="0">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s" s="0">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s" s="0">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s" s="0">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s" s="0">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s" s="0">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s" s="0">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s" s="0">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s" s="0">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s" s="0">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s" s="0">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s" s="0">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s" s="0">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s" s="0">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s" s="0">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s" s="0">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s" s="0">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s" s="0">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s" s="0">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s" s="0">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s" s="0">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s" s="0">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s" s="0">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s" s="0">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s" s="0">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s" s="0">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s" s="0">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s" s="0">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s" s="0">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s" s="0">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s" s="0">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s" s="0">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s" s="0">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s" s="0">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s" s="0">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s" s="0">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s" s="0">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s" s="0">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s" s="0">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s" s="0">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s" s="0">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s" s="0">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s" s="0">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s" s="0">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s" s="0">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s" s="0">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s" s="0">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s" s="0">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s" s="0">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s" s="0">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s" s="0">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s" s="0">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s" s="0">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s" s="0">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s" s="0">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s" s="0">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s" s="0">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s" s="0">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s" s="0">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s" s="0">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s" s="0">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s" s="0">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s" s="0">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s" s="0">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s" s="0">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s" s="0">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s" s="0">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s" s="0">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s" s="0">
-        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="18">
   <si>
     <t>yco71304@maildrop.cc</t>
   </si>
@@ -41,6 +41,33 @@
   </si>
   <si>
     <t>Picked</t>
+  </si>
+  <si>
+    <t>MissWyattRau@yopmail.com</t>
+  </si>
+  <si>
+    <t>BartonPouros@yopmail.com</t>
+  </si>
+  <si>
+    <t>yco2606231435m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606231435m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606231438m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606231438m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606231441m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606231441m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Udaan Sector Elite Youth Club</t>
   </si>
 </sst>
 </file>
@@ -1261,7 +1288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1">
@@ -1444,6 +1471,16 @@
         <is>
           <t>HassieBrown@yopmail.com</t>
         </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1457,7 +1494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1543,6 +1580,72 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="25">
   <si>
     <t>yco71304@maildrop.cc</t>
   </si>
@@ -68,6 +68,27 @@
   </si>
   <si>
     <t>Udaan Sector Elite Youth Club</t>
+  </si>
+  <si>
+    <t>yco2606232131m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606232131m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606232132m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606232132m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606232134m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606232134m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Prerana Colony Apex Youth Club</t>
   </si>
 </sst>
 </file>
@@ -1494,7 +1515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1646,6 +1667,72 @@
         <v>8</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="39">
   <si>
     <t>yco71304@maildrop.cc</t>
   </si>
@@ -110,6 +110,27 @@
   </si>
   <si>
     <t>Sahyog Vihar Nova Youth Club</t>
+  </si>
+  <si>
+    <t>yco2606241929m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606241929m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606241932m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606241932m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606241934m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606241934m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Nai Disha Enclave Beta Youth Club</t>
   </si>
 </sst>
 </file>
@@ -1536,7 +1557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1820,6 +1841,72 @@
         <v>8</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="40">
   <si>
     <t>yco71304@maildrop.cc</t>
   </si>
@@ -131,6 +131,9 @@
   </si>
   <si>
     <t>Nai Disha Enclave Beta Youth Club</t>
+  </si>
+  <si>
+    <t>TheronMurazik@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1351,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1">
@@ -1544,6 +1547,11 @@
     <row r="28">
       <c r="A28" t="s" s="0">
         <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="42">
   <si>
     <t>yco71304@maildrop.cc</t>
   </si>
@@ -134,6 +134,12 @@
   </si>
   <si>
     <t>TheronMurazik@maildrop.cc</t>
+  </si>
+  <si>
+    <t>vincestiedemann@yopmail.com</t>
+  </si>
+  <si>
+    <t>hermandouglasjr@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1354,7 +1360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1">
@@ -1552,6 +1558,16 @@
     <row r="29">
       <c r="A29" t="s" s="0">
         <v>39</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="43">
   <si>
     <t>yco71304@maildrop.cc</t>
   </si>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t>hermandouglasjr@yopmail.com</t>
+  </si>
+  <si>
+    <t>msquentinwisozk@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1360,7 +1363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1">
@@ -1568,6 +1571,11 @@
     <row r="31">
       <c r="A31" t="s" s="0">
         <v>41</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
